--- a/data/event_en.xlsx
+++ b/data/event_en.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\Mile_CV\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59EE63B4-EC74-4CE3-8F4E-149D95FBD9AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B516F095-5C84-4EF6-9089-3CF31F31C665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>what</t>
   </si>
@@ -82,6 +82,18 @@
   </si>
   <si>
     <t>\href{https://www.youtube.com/watch?v=dNqxY_fGKwE}{Universidad El Bosque}</t>
+  </si>
+  <si>
+    <t>Sept. 25, 2025</t>
+  </si>
+  <si>
+    <t>Universidad El Bosque</t>
+  </si>
+  <si>
+    <t>International Symposium: Acting Before Harm: Preventing Child Sexual Abuse and Exploitation of Children</t>
+  </si>
+  <si>
+    <t>\href{https://www.youtube.com/watch?v=-rzZiyxiTyI}{Universidad El Bosque}</t>
   </si>
 </sst>
 </file>
@@ -523,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.109375" customWidth="1"/>
@@ -555,16 +567,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -572,42 +584,59 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E5" s="1" t="s">
+    <row r="6" spans="1:5" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E9" s="2"/>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
